--- a/Post-Experiment/NASA-TLX/ALL_TLX_DATA.xlsx
+++ b/Post-Experiment/NASA-TLX/ALL_TLX_DATA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juliasantaniello/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juliasantaniello/Desktop/fNIRS-2-RL/Post-Experiment/NASA-TLX/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08CEA39-EA71-4A48-937F-06731A9EFDBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3414CCD9-663F-224C-AC85-0A9FE9A7FA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1960" yWindow="2100" windowWidth="28040" windowHeight="11260" xr2:uid="{C03420E4-ECF1-B549-A473-95F31F5500A6}"/>
+    <workbookView xWindow="9220" yWindow="2240" windowWidth="28040" windowHeight="11260" xr2:uid="{C03420E4-ECF1-B549-A473-95F31F5500A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="51">
   <si>
     <t>Caffiene Today</t>
   </si>
@@ -185,12 +185,18 @@
   <si>
     <t>Averages</t>
   </si>
+  <si>
+    <t>T-Test Against Condition Pair (e.g.LW/LP)</t>
+  </si>
+  <si>
+    <t>0+D3:D27</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -224,6 +230,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -255,36 +268,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Heading 1" xfId="1" builtinId="16"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="25">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -717,6 +713,24 @@
         <scheme val="none"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -731,44 +745,44 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7D7D2A7C-88F9-774E-AB2F-DABE412B09F4}" name="Table1" displayName="Table1" ref="A2:AK27" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7D7D2A7C-88F9-774E-AB2F-DABE412B09F4}" name="Table1" displayName="Table1" ref="A2:AK27" totalsRowShown="0" headerRowDxfId="24">
   <autoFilter ref="A2:AK27" xr:uid="{7D7D2A7C-88F9-774E-AB2F-DABE412B09F4}"/>
   <tableColumns count="37">
     <tableColumn id="1" xr3:uid="{DACD049F-E286-DD40-A3F4-75146F9515CA}" name="Participant Number"/>
-    <tableColumn id="2" xr3:uid="{C53CBAA1-2FFD-8143-8531-4277C0FC7E5C}" name="LW - Mental Demand" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{DCBC0F8C-628C-B547-96B6-114671E527F9}" name="LP - Mental Demand" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{C53CBAA1-2FFD-8143-8531-4277C0FC7E5C}" name="LW - Mental Demand" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{DCBC0F8C-628C-B547-96B6-114671E527F9}" name="LP - Mental Demand" dataDxfId="22"/>
     <tableColumn id="4" xr3:uid="{E67BD103-2EBA-CB42-A325-95653471596D}" name="FW - Mental Demand"/>
-    <tableColumn id="5" xr3:uid="{ABD135F5-F9E4-1B4E-BCFD-0BBFBECCF309}" name="FP - Mental Demand" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{ABD135F5-F9E4-1B4E-BCFD-0BBFBECCF309}" name="FP - Mental Demand" dataDxfId="21"/>
     <tableColumn id="6" xr3:uid="{5963C75B-42C7-034C-9570-FEDA4C5D218E}" name="RW - Mental Demand"/>
-    <tableColumn id="7" xr3:uid="{084F74D6-B8EC-494B-B131-C18DFDB90D8E}" name="RP - Mental Demand" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{AAFBCC4C-0D9A-BA4E-B278-2A3178F8BD0E}" name="LW - Physical Demand" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{5DC7D2BB-6CB0-564E-AE1B-4D4FCD60C77E}" name="LP - Physical Demand" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{B8DB4369-55AA-D946-9506-3305E648E01D}" name="FW - Phys Demand" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{1227A8E6-4396-9D42-B451-30F7F4016D5D}" name="FP - Phys Demand" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{084F74D6-B8EC-494B-B131-C18DFDB90D8E}" name="RP - Mental Demand" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{AAFBCC4C-0D9A-BA4E-B278-2A3178F8BD0E}" name="LW - Physical Demand" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{5DC7D2BB-6CB0-564E-AE1B-4D4FCD60C77E}" name="LP - Physical Demand" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{B8DB4369-55AA-D946-9506-3305E648E01D}" name="FW - Phys Demand" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{1227A8E6-4396-9D42-B451-30F7F4016D5D}" name="FP - Phys Demand" dataDxfId="16"/>
     <tableColumn id="12" xr3:uid="{28547851-9C21-E540-AC5B-B737C59E38C9}" name="RW - Phys Demand"/>
     <tableColumn id="13" xr3:uid="{C8543BD8-C14F-404E-A8B6-14A01CB087D1}" name="RP - Phys Demand"/>
-    <tableColumn id="14" xr3:uid="{47824343-FC29-3F40-8B60-C403201A743C}" name="LW - Hurry" dataDxfId="16"/>
-    <tableColumn id="15" xr3:uid="{47742664-8BD1-314F-A031-6BF90E73E7DB}" name="LP - Hurry" dataDxfId="15"/>
-    <tableColumn id="16" xr3:uid="{0F1C82A7-C13A-AA4D-BEDA-F45055AA6BEA}" name="FW - Hurry" dataDxfId="14"/>
-    <tableColumn id="17" xr3:uid="{CAB2DC23-86FF-2248-BDF4-C537D273E10A}" name="FP - Hurry" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{47824343-FC29-3F40-8B60-C403201A743C}" name="LW - Hurry" dataDxfId="15"/>
+    <tableColumn id="15" xr3:uid="{47742664-8BD1-314F-A031-6BF90E73E7DB}" name="LP - Hurry" dataDxfId="14"/>
+    <tableColumn id="16" xr3:uid="{0F1C82A7-C13A-AA4D-BEDA-F45055AA6BEA}" name="FW - Hurry" dataDxfId="13"/>
+    <tableColumn id="17" xr3:uid="{CAB2DC23-86FF-2248-BDF4-C537D273E10A}" name="FP - Hurry" dataDxfId="12"/>
     <tableColumn id="18" xr3:uid="{F7976F1C-BA4B-DB4E-9013-76E7A115DD66}" name="RW - Hurry"/>
     <tableColumn id="19" xr3:uid="{A5D232A2-DCE9-714F-A135-E8CDBA5A45E5}" name="RP - Hurry"/>
-    <tableColumn id="20" xr3:uid="{7CD6F9FC-7A6B-FC4C-A162-0989DB910098}" name="LW - Work" dataDxfId="12"/>
-    <tableColumn id="21" xr3:uid="{8E5FCBA1-7CE2-E143-A4A7-0EB73059471B}" name="LP - Work" dataDxfId="11"/>
-    <tableColumn id="22" xr3:uid="{5CB3C5E7-4C31-F748-ACBF-CD3725E2F0FD}" name="FW - Work" dataDxfId="10"/>
-    <tableColumn id="23" xr3:uid="{8ADABBFB-8A3D-BC4A-9351-D8164A3A0622}" name="FP - Work" dataDxfId="9"/>
+    <tableColumn id="20" xr3:uid="{7CD6F9FC-7A6B-FC4C-A162-0989DB910098}" name="LW - Work" dataDxfId="11"/>
+    <tableColumn id="21" xr3:uid="{8E5FCBA1-7CE2-E143-A4A7-0EB73059471B}" name="LP - Work" dataDxfId="10"/>
+    <tableColumn id="22" xr3:uid="{5CB3C5E7-4C31-F748-ACBF-CD3725E2F0FD}" name="FW - Work" dataDxfId="9"/>
+    <tableColumn id="23" xr3:uid="{8ADABBFB-8A3D-BC4A-9351-D8164A3A0622}" name="FP - Work" dataDxfId="8"/>
     <tableColumn id="24" xr3:uid="{78313B79-31E2-E44A-B5F0-0A08788C46C7}" name="RW - Work"/>
     <tableColumn id="25" xr3:uid="{16115C20-F949-E34E-834E-7ED741FCF96F}" name="RP - Work"/>
-    <tableColumn id="26" xr3:uid="{AEF995AA-1882-C54B-8E2D-6D7F56EC2A2D}" name="LW - Stress" dataDxfId="8"/>
-    <tableColumn id="27" xr3:uid="{100273EB-B9C3-1843-899F-BDE56499804D}" name="LP - Stress" dataDxfId="7"/>
-    <tableColumn id="28" xr3:uid="{6BF63FBE-C8AD-6949-88C3-AB4319CFB90C}" name="FW - Stress" dataDxfId="6"/>
-    <tableColumn id="29" xr3:uid="{2264E794-B2D2-0B45-94E1-0F3176E82D93}" name="FP - Stress" dataDxfId="5"/>
+    <tableColumn id="26" xr3:uid="{AEF995AA-1882-C54B-8E2D-6D7F56EC2A2D}" name="LW - Stress" dataDxfId="7"/>
+    <tableColumn id="27" xr3:uid="{100273EB-B9C3-1843-899F-BDE56499804D}" name="LP - Stress" dataDxfId="6"/>
+    <tableColumn id="28" xr3:uid="{6BF63FBE-C8AD-6949-88C3-AB4319CFB90C}" name="FW - Stress" dataDxfId="5"/>
+    <tableColumn id="29" xr3:uid="{2264E794-B2D2-0B45-94E1-0F3176E82D93}" name="FP - Stress" dataDxfId="4"/>
     <tableColumn id="30" xr3:uid="{C3B77506-20D2-5F40-83EA-CA6C0A69F1D6}" name="RW - Stress"/>
     <tableColumn id="31" xr3:uid="{48AFA9B8-2325-AE4B-834F-AC85C58A063F}" name="RP - Stress"/>
-    <tableColumn id="32" xr3:uid="{042D2C62-3CD0-314F-BE86-0137E7A87D9F}" name="LW - Unsuccess" dataDxfId="4"/>
-    <tableColumn id="33" xr3:uid="{31BC7A62-F8E7-2F4A-98C8-F30670D4CEA3}" name="LP - Unsuccess" dataDxfId="3"/>
-    <tableColumn id="34" xr3:uid="{F58F763F-71D0-1C4F-846C-2691C235A8A5}" name="FW - Unsuccess" dataDxfId="2"/>
-    <tableColumn id="35" xr3:uid="{CB84A151-9C93-6346-A010-A4C485C415C9}" name="FP - Unsuccess" dataDxfId="1"/>
+    <tableColumn id="32" xr3:uid="{042D2C62-3CD0-314F-BE86-0137E7A87D9F}" name="LW - Unsuccess" dataDxfId="3"/>
+    <tableColumn id="33" xr3:uid="{31BC7A62-F8E7-2F4A-98C8-F30670D4CEA3}" name="LP - Unsuccess" dataDxfId="2"/>
+    <tableColumn id="34" xr3:uid="{F58F763F-71D0-1C4F-846C-2691C235A8A5}" name="FW - Unsuccess" dataDxfId="1"/>
+    <tableColumn id="35" xr3:uid="{CB84A151-9C93-6346-A010-A4C485C415C9}" name="FP - Unsuccess" dataDxfId="0"/>
     <tableColumn id="36" xr3:uid="{6702B7AA-698B-5A48-8517-E6AD02D3D85A}" name="RW - Unsuccess"/>
     <tableColumn id="37" xr3:uid="{DF15D7EA-5DDA-EE42-977E-4D7F64FB9A8D}" name="RP - Unsuccess"/>
   </tableColumns>
@@ -1093,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD27C28-AF3C-374D-AA09-CF09B2000583}">
-  <dimension ref="A1:AK55"/>
+  <dimension ref="A1:BB55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.33203125" customWidth="1"/>
@@ -1263,8 +1277,8 @@
       <c r="C3" s="1">
         <v>75</v>
       </c>
-      <c r="D3" s="1">
-        <v>0</v>
+      <c r="D3" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>45</v>
@@ -2807,7 +2821,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2914,7 +2928,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3025,7 +3039,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3116,7 +3130,7 @@
       </c>
       <c r="AK19" s="2"/>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3229,7 +3243,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3342,7 +3356,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3455,7 +3469,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3568,7 +3582,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3681,7 +3695,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3794,7 +3808,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>46</v>
       </c>
@@ -3871,7 +3885,7 @@
       </c>
       <c r="AK26" s="2"/>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>25</v>
       </c>
@@ -3984,7 +3998,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:54" x14ac:dyDescent="0.2">
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
@@ -4014,7 +4028,7 @@
       <c r="AJ28" s="2"/>
       <c r="AK28" s="1"/>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -4127,7 +4141,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:54" x14ac:dyDescent="0.2">
       <c r="B30" s="1">
         <f>AVERAGE(B3:B27)</f>
         <v>13.615384615384615</v>
@@ -4138,7 +4152,7 @@
       </c>
       <c r="D30" s="1">
         <f t="shared" si="0"/>
-        <v>19.176470588235293</v>
+        <v>20.375</v>
       </c>
       <c r="E30" s="1">
         <f t="shared" si="0"/>
@@ -4273,7 +4287,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:54" x14ac:dyDescent="0.2">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -4311,43 +4325,168 @@
       <c r="AJ31" s="2"/>
       <c r="AK31" s="1"/>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="2"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-      <c r="Z32" s="1"/>
-      <c r="AA32" s="2"/>
-      <c r="AB32" s="2"/>
-      <c r="AC32" s="1"/>
-      <c r="AD32" s="1"/>
-      <c r="AE32" s="1"/>
-      <c r="AF32" s="1"/>
-      <c r="AG32" s="2"/>
-      <c r="AH32" s="2"/>
-      <c r="AI32" s="1"/>
-      <c r="AJ32" s="1"/>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="5">
+        <f>_xlfn.T.TEST(Table1[LW - Mental Demand],Table1[LP - Mental Demand],2,3)</f>
+        <v>1.2474675479997605E-9</v>
+      </c>
+      <c r="C32" s="1">
+        <f>_xlfn.T.TEST(Table1[LP - Mental Demand],Table1[FW - Mental Demand],2,3)</f>
+        <v>5.9014224693143578E-8</v>
+      </c>
+      <c r="D32" s="5">
+        <f>_xlfn.T.TEST(Table1[FW - Mental Demand],Table1[FP - Mental Demand],2,3)</f>
+        <v>3.5949489684652981E-3</v>
+      </c>
+      <c r="E32" s="1">
+        <f>_xlfn.T.TEST(Table1[FP - Mental Demand],Table1[RW - Mental Demand],2,3)</f>
+        <v>1.1087961692481621E-2</v>
+      </c>
+      <c r="F32" s="5">
+        <f>_xlfn.T.TEST(Table1[RW - Mental Demand],Table1[RP - Mental Demand],2,3)</f>
+        <v>8.3312187312084378E-4</v>
+      </c>
+      <c r="G32" s="1">
+        <f>_xlfn.T.TEST(Table1[RP - Mental Demand],Table1[LW - Physical Demand],2,3)</f>
+        <v>3.9744453856616719E-6</v>
+      </c>
+      <c r="H32" s="5">
+        <f>_xlfn.T.TEST(Table1[LW - Physical Demand],Table1[LP - Physical Demand],2,3)</f>
+        <v>5.8933251428902695E-3</v>
+      </c>
+      <c r="I32" s="1">
+        <f>_xlfn.T.TEST(Table1[LP - Physical Demand],Table1[FW - Phys Demand],2,3)</f>
+        <v>2.0197440643986977E-3</v>
+      </c>
+      <c r="J32" s="1">
+        <f>_xlfn.T.TEST(Table1[FW - Phys Demand],Table1[FP - Phys Demand],2,3)</f>
+        <v>0.30570903689574674</v>
+      </c>
+      <c r="K32" s="1">
+        <f>_xlfn.T.TEST(Table1[FP - Phys Demand],Table1[RW - Phys Demand],2,3)</f>
+        <v>0.4525663515898426</v>
+      </c>
+      <c r="L32" s="5">
+        <f>_xlfn.T.TEST(Table1[RW - Phys Demand],Table1[RP - Phys Demand],2,3)</f>
+        <v>1.0193584699457031E-2</v>
+      </c>
+      <c r="M32" s="1">
+        <f>_xlfn.T.TEST(Table1[RP - Phys Demand],Table1[LW - Hurry],2,3)</f>
+        <v>3.5914067699842026E-2</v>
+      </c>
+      <c r="N32" s="5">
+        <f>_xlfn.T.TEST(Table1[LW - Hurry],Table1[LP - Hurry],2,3)</f>
+        <v>1.8698495655635299E-5</v>
+      </c>
+      <c r="O32" s="1">
+        <f>_xlfn.T.TEST(Table1[LP - Hurry],Table1[FW - Hurry],2,3)</f>
+        <v>6.6967170024392452E-4</v>
+      </c>
+      <c r="P32" s="1">
+        <f>_xlfn.T.TEST(Table1[FW - Hurry],Table1[FP - Hurry],2,3)</f>
+        <v>0.2055269139155643</v>
+      </c>
+      <c r="Q32" s="1">
+        <f>_xlfn.T.TEST(Table1[FP - Hurry],Table1[RW - Hurry],2,3)</f>
+        <v>0.61168205132106812</v>
+      </c>
+      <c r="R32" s="1">
+        <f>_xlfn.T.TEST(Table1[RW - Hurry],Table1[RP - Hurry],2,3)</f>
+        <v>0.47042114291923709</v>
+      </c>
+      <c r="S32" s="1">
+        <f>_xlfn.T.TEST(Table1[RP - Hurry],Table1[LW - Work],2,3)</f>
+        <v>3.4086753400538981E-2</v>
+      </c>
+      <c r="T32" s="5">
+        <f>_xlfn.T.TEST(Table1[LW - Work],Table1[LP - Work],2,3)</f>
+        <v>3.695075703735635E-6</v>
+      </c>
+      <c r="U32" s="1">
+        <f>_xlfn.T.TEST(Table1[LP - Work],Table1[FW - Work],2,3)</f>
+        <v>8.4014196620079961E-6</v>
+      </c>
+      <c r="V32" s="5">
+        <f>_xlfn.T.TEST(Table1[FW - Work],Table1[FP - Work],2,3)</f>
+        <v>4.2528375191166874E-2</v>
+      </c>
+      <c r="W32" s="1">
+        <f>_xlfn.T.TEST(Table1[FP - Work],Table1[RW - Work],2,3)</f>
+        <v>1.5722658426954493E-2</v>
+      </c>
+      <c r="X32" s="5">
+        <f>_xlfn.T.TEST(Table1[RW - Work],Table1[RP - Work],2,3)</f>
+        <v>3.7885627128647643E-3</v>
+      </c>
+      <c r="Y32" s="1">
+        <f>_xlfn.T.TEST(Table1[RP - Work],Table1[LW - Stress],2,3)</f>
+        <v>1.822983197215235E-2</v>
+      </c>
+      <c r="Z32" s="5">
+        <f>_xlfn.T.TEST(Table1[LW - Stress],Table1[LP - Stress],2,3)</f>
+        <v>5.1155156912644872E-5</v>
+      </c>
+      <c r="AA32" s="1">
+        <f>_xlfn.T.TEST(Table1[LP - Stress],Table1[FW - Stress],2,3)</f>
+        <v>6.1963188796634991E-4</v>
+      </c>
+      <c r="AB32" s="1">
+        <f>_xlfn.T.TEST(Table1[FW - Stress],Table1[FP - Stress],2,3)</f>
+        <v>9.7894282492786089E-2</v>
+      </c>
+      <c r="AC32" s="1">
+        <f>_xlfn.T.TEST(Table1[FP - Stress],Table1[RW - Stress],2,3)</f>
+        <v>0.11548015242611899</v>
+      </c>
+      <c r="AD32" s="1">
+        <f>_xlfn.T.TEST(Table1[RW - Stress],Table1[RP - Stress],2,3)</f>
+        <v>0.85763434978534214</v>
+      </c>
+      <c r="AE32" s="1">
+        <f>_xlfn.T.TEST(Table1[RP - Stress],Table1[LW - Unsuccess],2,3)</f>
+        <v>0.95526826424550271</v>
+      </c>
+      <c r="AF32" s="5">
+        <f>_xlfn.T.TEST(Table1[LW - Unsuccess],Table1[LP - Unsuccess],2,3)</f>
+        <v>3.5947287275497051E-4</v>
+      </c>
+      <c r="AG32" s="1">
+        <f>_xlfn.T.TEST(Table1[LP - Unsuccess],Table1[FW - Unsuccess],2,3)</f>
+        <v>2.5737810268080261E-4</v>
+      </c>
+      <c r="AH32" s="1">
+        <f>_xlfn.T.TEST(Table1[FW - Unsuccess],Table1[FP - Unsuccess],2,3)</f>
+        <v>0.1426613266771993</v>
+      </c>
+      <c r="AI32" s="1">
+        <f>_xlfn.T.TEST(Table1[FP - Unsuccess],Table1[RW - Unsuccess],2,3)</f>
+        <v>8.1794795630504402E-2</v>
+      </c>
+      <c r="AJ32" s="1">
+        <f>_xlfn.T.TEST(Table1[RW - Unsuccess],Table1[RP - Unsuccess],2,3)</f>
+        <v>0.49978700884509908</v>
+      </c>
       <c r="AK32" s="1"/>
+      <c r="AL32" s="1"/>
+      <c r="AM32" s="1"/>
+      <c r="AN32" s="1"/>
+      <c r="AO32" s="1"/>
+      <c r="AP32" s="1"/>
+      <c r="AQ32" s="1"/>
+      <c r="AR32" s="1"/>
+      <c r="AS32" s="1"/>
+      <c r="AT32" s="1"/>
+      <c r="AU32" s="1"/>
+      <c r="AV32" s="1"/>
+      <c r="AW32" s="1"/>
+      <c r="AX32" s="1"/>
+      <c r="AY32" s="1"/>
+      <c r="AZ32" s="1"/>
+      <c r="BA32" s="1"/>
+      <c r="BB32" s="1"/>
     </row>
     <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B33" s="1"/>
@@ -4425,6 +4564,9 @@
       <c r="AJ34" s="2"/>
       <c r="AK34" s="2"/>
     </row>
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="B35" s="5"/>
+    </row>
     <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
